--- a/stories/arbres/ATOM-REL.CON.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rania peint à table avec Nino. Papa est près d'eux. Rania passe trop vite. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Nino a les yeux mouillés. Papa s'approche. Papa dit : tu peux dire pardon. Rania dit : pardon, Nino. Papa dit : tu peux proposer un geste. Rania tend une feuille neuve. C'est un geste simple. Nino prend la feuille. Il reste un peu triste. Papa dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, Rania bouscule une tour de cubes. Les cubes roulent. Rania dit encore : pardon. Elle tend un cube. C'est un geste. La peine reste un peu. Papa laisse du temps. Ils reconstruisent doucement.</t>
+          <t>Rania peint à table avec Nino. Papa est près d'eux. Rania passe trop vite. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Nino a les yeux mouillés. Papa s'approche. Tu peux dire pardon. Pardon, Nino. Tu peux proposer un geste. Rania tend une feuille neuve. C'est un geste simple. Nino prend la feuille. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, Rania bouscule une tour de cubes. Les cubes roulent. Rania dit encore : pardon. Elle tend un cube. C'est un geste. La peine reste un peu. Papa laisse du temps. Ils reconstruisent doucement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Rania peint à table avec Nino. Papa est près d'eux. Rania passe trop vite. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Nino a les yeux mouillés. Papa s'approche.
+papa|Tu peux dire pardon.
+enfant-f|Pardon, Nino.
+papa|Tu peux proposer un geste.
+narrateur|Rania tend une feuille neuve. C'est un geste simple. Nino prend la feuille. Il reste un peu triste.
+papa|La peine reste un peu.
+narrateur|Le pardon n'efface pas tout de suite. Plus tard, Rania bouscule une tour de cubes. Les cubes roulent. Rania dit encore : pardon. Elle tend un cube. C'est un geste. La peine reste un peu. Papa laisse du temps. Ils reconstruisent doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le dessin de Nino est mouillé. Que fait Rania ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Rania a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La tour grandit tout doucement. Papa reste assis près d'eux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Le pardon n'efface pas tout de suite. Plus tard, Rania bouscule une tour de cubes. Les cubes roulent. Rania dit encore : pardon. Elle tend un cube. C'est un geste. La peine reste un peu. Papa laisse du temps. Ils reconstruisent doucement.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Le dessin de Nino est mouillé. Que fait Rania ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Rania a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|La tour grandit tout doucement. Papa reste assis près d'eux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rania dit pardon et propose un geste</t>
+          <t>Le bocal bleu et la feuille neuve</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina renverse l'eau sur le dessin de Nino. Elle dit pardon et tend une feuille neuve. Plus tard, sa tour de cubes tombe. Encore pardon, encore un geste. La peine reste un peu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rania peint à table avec Nino. Papa est près d'eux. Rania passe trop vite. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Nino a les yeux mouillés. Papa s'approche. Tu peux dire pardon. Pardon, Nino. Tu peux proposer un geste. Rania tend une feuille neuve. C'est un geste simple. Nino prend la feuille. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, Rania bouscule une tour de cubes. Les cubes roulent. Rania dit encore : pardon. Elle tend un cube. C'est un geste. La peine reste un peu. Papa laisse du temps. Ils reconstruisent doucement.</t>
+          <t>Le bocal d'eau tourne au bleu. Des ronds bleus montent, tout lents. Le journal sous le papier craque. Il sent l'encre un peu sèche. La chaise de papa grince. Un pinceau goutte sur le bord. Une goutte fait un point rond. Le parquet est un peu froid sous les pieds. Une chaussette de Nina a glissé. Elle fait un petit tas gris. Tu as vu les ronds bleus, Nina ? Oui, papa. Ils montent. Nino dessine à côté. Son bateau est presque fini. En ce moment, Nina passe près du bocal. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Le bateau bave, tout pâle. Nino a les yeux mouillés. Il est triste. Nino a de la peine, Nina. Tu peux dire pardon. Pardon, Nino. Tu peux proposer un geste. Nina tend une feuille neuve. La feuille est blanche et lisse. Tu peux recommencer dessus. C'est un geste simple. Nino prend la feuille. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Nino s'assoit près de papa. Nina attend, les mains calmes. Nino passe le doigt sur le papier mouillé. Tu as le temps, Nino. Le bateau pâle ne bouge plus. On laisse du temps à Nino. Tu attends avec moi ? Oui, papa. Les ronds bleus s'arrêtent. Le journal n'est plus craquant. Plus tard, Nina pose des cubes. Les cubes sont rouges et gris. Nino a fait une petite tour. Nina passe trop vite. Les cubes roulent. Un cube rouge tapote le parquet. Pardon, Nino. Je te tends un cube. C'est un geste. Nino le prend. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Nina. C'est du bon travail. Nino a encore un peu de peine. C'est normal. Ils reconstruisent doucement. La tour est plus petite. Le pinceau sèche sur le journal.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Rania peint à table avec Nino. Papa est près d'eux. Rania passe trop vite. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Nino a les yeux mouillés. Papa s'approche.
+          <t>narrateur|Le bocal d'eau tourne au bleu.
+narrateur|Des ronds bleus montent, tout lents.
+narrateur|Le journal sous le papier craque.
+narrateur|Il sent l'encre un peu sèche.
+narrateur|La chaise de papa grince.
+narrateur|Un pinceau goutte sur le bord.
+narrateur|Une goutte fait un point rond.
+narrateur|Le parquet est un peu froid sous les pieds.
+narrateur|Une chaussette de Nina a glissé.
+narrateur|Elle fait un petit tas gris.
+papa|Tu as vu les ronds bleus, Nina ?
+enfant-f|Oui, papa.
+enfant-f|Ils montent.
+papa|Nino dessine à côté.
+papa|Son bateau est presque fini.
+narrateur|En ce moment, Nina passe près du bocal.
+narrateur|L'eau tombe sur le dessin de Nino.
+narrateur|Le papier est mouillé.
+narrateur|Le bateau bave, tout pâle.
+narrateur|Nino a les yeux mouillés.
+narrateur|Il est triste.
+papa|Nino a de la peine, Nina.
 papa|Tu peux dire pardon.
 enfant-f|Pardon, Nino.
 papa|Tu peux proposer un geste.
-narrateur|Rania tend une feuille neuve. C'est un geste simple. Nino prend la feuille. Il reste un peu triste.
+narrateur|Nina tend une feuille neuve.
+narrateur|La feuille est blanche et lisse.
+enfant-f|Tu peux recommencer dessus.
+narrateur|C'est un geste simple.
+narrateur|Nino prend la feuille.
+narrateur|Il reste un peu triste.
 papa|La peine reste un peu.
-narrateur|Le pardon n'efface pas tout de suite. Plus tard, Rania bouscule une tour de cubes. Les cubes roulent. Rania dit encore : pardon. Elle tend un cube. C'est un geste. La peine reste un peu. Papa laisse du temps. Ils reconstruisent doucement.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Le pardon n'efface pas tout de suite.
+narrateur|Nino s'assoit près de papa.
+narrateur|Nina attend, les mains calmes.
+narrateur|Nino passe le doigt sur le papier mouillé.
+papa|Tu as le temps, Nino.
+narrateur|Le bateau pâle ne bouge plus.
+papa|On laisse du temps à Nino.
+papa|Tu attends avec moi ?
+enfant-f|Oui, papa.
+narrateur|Les ronds bleus s'arrêtent.
+narrateur|Le journal n'est plus craquant.
+narrateur|Plus tard, Nina pose des cubes.
+narrateur|Les cubes sont rouges et gris.
+narrateur|Nino a fait une petite tour.
+narrateur|Nina passe trop vite.
+narrateur|Les cubes roulent.
+narrateur|Un cube rouge tapote le parquet.
+enfant-f|Pardon, Nino.
+enfant-f|Je te tends un cube.
+narrateur|C'est un geste.
+narrateur|Nino le prend.
+narrateur|La peine reste un peu.
+papa|Tu as dit pardon, encore.
+papa|Tu as proposé un geste.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+papa|Nino a encore un peu de peine.
+papa|C'est normal.
+narrateur|Ils reconstruisent doucement.
+narrateur|La tour est plus petite.
+narrateur|Le pinceau sèche sur le journal.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>eau_tombe,cubes_tombent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1418,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le dessin de Nino est mouillé. Que fait Rania ?</t>
+          <t>Le dessin de Nino est mouillé. Que fait Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1574,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le dessin de Nino est mouillé. Que fait Rania ?</t>
+          <t>narrateur|Le dessin de Nino est mouillé.
+narrateur|Que fait Nina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1603,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rania a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa est là.</t>
+          <t>Nina a dit pardon. Elle a proposé un geste. Elle a tendu une feuille neuve. Bravo, Nina. C'est du bon travail. La peine de Nino reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1747,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Rania a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa est là.</t>
+          <t>narrateur|Nina a dit pardon.
+narrateur|Elle a proposé un geste.
+narrateur|Elle a tendu une feuille neuve.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+papa|La peine de Nino reste un peu.
+enfant-f|J'ai dit pardon.
+papa|Oui.
+papa|Et tu as attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La tour grandit tout doucement. Papa reste assis près d'eux.</t>
+          <t>La tour grandit tout doucement. Un cube rouge, un cube gris. On reste assis près de Nino ? Oui, papa. La feuille neuve est encore blanche. La peine reste un peu. Je laisse du temps. Oui. C'est bien. Le bocal n'est plus bleu. L'eau est calme. La chaussette grise attend encore. On la remettra plus tard. D'accord, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1923,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La tour grandit tout doucement. Papa reste assis près d'eux.</t>
+          <t>narrateur|La tour grandit tout doucement.
+narrateur|Un cube rouge, un cube gris.
+papa|On reste assis près de Nino ?
+enfant-f|Oui, papa.
+papa|La feuille neuve est encore blanche.
+papa|La peine reste un peu.
+enfant-f|Je laisse du temps.
+papa|Oui.
+papa|C'est bien.
+narrateur|Le bocal n'est plus bleu.
+narrateur|L'eau est calme.
+narrateur|La chaussette grise attend encore.
+papa|On la remettra plus tard.
+enfant-f|D'accord, papa.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu une feuille. Bravo. Tu as fait du bon travail. Le pinceau est sec, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2104,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit pardon.
+enfant-f|J'ai tendu une feuille.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pinceau est sec, maintenant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2169,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le bocal d'eau tourne au bleu. Des ronds bleus montent, tout lents. Le journal sous le papier craque. Il sent l'encre un peu sèche. La chaise de papa grince. Un pinceau goutte sur le bord. Une goutte fait un point rond. Le parquet est un peu froid sous les pieds. Une chaussette de Nina a glissé. Elle fait un petit tas gris. Tu as vu les ronds bleus, Nina ? Oui, papa. Ils montent. Nino dessine à côté. Son bateau est presque fini. En ce moment, Nina passe près du bocal. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Le bateau bave, tout pâle. Nino a les yeux mouillés. Il est triste. Nino a de la peine, Nina. Tu peux dire pardon. Pardon, Nino. Tu peux proposer un geste. Nina tend une feuille neuve. La feuille est blanche et lisse. Tu peux recommencer dessus. C'est un geste simple. Nino prend la feuille. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Nino s'assoit près de papa. Nina attend, les mains calmes. Nino passe le doigt sur le papier mouillé. Tu as le temps, Nino. Le bateau pâle ne bouge plus. On laisse du temps à Nino. Tu attends avec moi ? Oui, papa. Les ronds bleus s'arrêtent. Le journal n'est plus craquant. Plus tard, Nina pose des cubes. Les cubes sont rouges et gris. Nino a fait une petite tour. Nina passe trop vite. Les cubes roulent. Un cube rouge tapote le parquet. Pardon, Nino. Je te tends un cube. C'est un geste. Nino le prend. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Nina. C'est du bon travail. Nino a encore un peu de peine. C'est normal. Ils reconstruisent doucement. La tour est plus petite. Le pinceau sèche sur le journal.</t>
+          <t>Le bocal d'eau tourne au bleu. Des ronds bleus montent, tout lents. Le journal sous le papier craque. Il sent l'encre un peu sèche. La chaise de papa grince. Un pinceau goutte sur le bord. Une goutte fait un point rond. Le parquet est un peu froid sous les pieds. Une chaussette de Nina a glissé. Elle fait un petit tas gris. Tu as vu les ronds bleus, Nina ? Oui, papa. Ils montent. Nino dessine à côté. Son bateau est presque fini. En ce moment, Nina passe près du bocal. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Le bateau bave, tout pâle. Nino a les yeux mouillés. Il est triste. Nino a de la peine, Nina. Tu peux dire pardon. Pardon, Nino. Tu peux proposer un geste. Nina tend une feuille neuve. La feuille est blanche et lisse. Tu peux recommencer dessus. C'est un geste simple. Nino prend la feuille. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Nino s'assoit près de papa. Nina attend, les mains calmes. Nino passe le doigt sur le papier mouillé. Tu as le temps, Nino. Le bateau pâle ne bouge plus. On laisse du temps à Nino. Tu attends avec moi ? Oui, papa. Les ronds bleus s'arrêtent. Le journal n'est plus craquant. Plus tard, Nina pose des cubes. Les cubes sont rouges et gris. Nino a fait une petite tour. Nina passe trop vite. Les cubes roulent. Un cube rouge tapote le parquet. Pardon, Nino. Je te tends un cube. C'est un geste. Nino le prend. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Nina. Nino a encore un peu de peine. C'est normal. Ils reconstruisent doucement. La tour est plus petite. Le pinceau sèche sur le journal.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rania peint à table avec Nino. Papa est près d'eux. Rania passe trop vite. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Nino a les yeux mouillés. Papa s'approche. Papa dit : tu peux dire &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Rania dit : pardon, Nino. Papa dit : tu peux proposer un geste. Rania tend une feuille neuve. C'est un geste simple. Nino prend la feuille. Il reste un peu triste. Papa dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, Rania bouscule une tour de cubes. Les cubes roulent. Rania dit encore : pardon. Elle tend un cube. C'est un geste. La peine reste un peu. Papa laisse du temps. Ils reconstruisent doucement.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bocal d'eau tourne au bleu. Des ronds bleus montent, tout lents. Le journal sous le papier craque. Il sent l'encre un peu sèche. La chaise de papa grince. Un pinceau goutte sur le bord. Une goutte fait un point rond. Le parquet est un peu froid sous les pieds. Une chaussette de Nina a glissé. Elle fait un petit tas gris. Tu as vu les ronds bleus, Nina ? Oui, papa. Ils montent. Nino dessine à côté. Son bateau est presque fini. En ce moment, Nina passe près du bocal. L'eau tombe sur le dessin de Nino. Le papier est mouillé. Le bateau bave, tout pâle. Nino a les yeux mouillés. Il est triste. Nino a de la peine, Nina. Tu peux dire pardon. Pardon, Nino. Tu peux proposer un geste. Nina tend une feuille neuve. La feuille est blanche et lisse. Tu peux recommencer dessus. C'est un geste simple. Nino prend la feuille. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Nino s'assoit près de papa. Nina attend, les mains calmes. Nino passe le doigt sur le papier mouillé. Tu as le temps, Nino. Le bateau pâle ne bouge plus. On laisse du temps à Nino. Tu attends avec moi ? Oui, papa. Les ronds bleus s'arrêtent. Le journal n'est plus craquant. Plus tard, Nina pose des cubes. Les cubes sont rouges et gris. Nino a fait une petite tour. Nina passe trop vite. Les cubes roulent. Un cube rouge tapote le parquet. Pardon, Nino. Je te tends un cube. C'est un geste. Nino le prend. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Nina. Nino a encore un peu de peine. C'est normal. Ils reconstruisent doucement. La tour est plus petite. Le pinceau sèche sur le journal.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1381,7 +1381,6 @@
 papa|Tu as dit pardon, encore.
 papa|Tu as proposé un geste.
 papa|Bravo, Nina.
-papa|C'est du bon travail.
 papa|Nino a encore un peu de peine.
 papa|C'est normal.
 narrateur|Ils reconstruisent doucement.
@@ -1423,7 +1422,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le dessin de Nino est mouillé. Que fait Rania ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le dessin de Nino est mouillé. Que fait Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1578,7 +1577,6 @@
 narrateur|Que fait Nina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1603,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a dit pardon. Elle a proposé un geste. Elle a tendu une feuille neuve. Bravo, Nina. C'est du bon travail. La peine de Nino reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
+          <t>Nina a dit pardon. Elle a proposé un geste. Elle a tendu une feuille neuve. Bravo, Nina. La peine de Nino reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rania a dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Elle a proposé un geste. La peine reste un peu. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a dit pardon. Elle a proposé un geste. Elle a tendu une feuille neuve. Bravo, Nina. La peine de Nino reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,14 +1749,12 @@
 narrateur|Elle a proposé un geste.
 narrateur|Elle a tendu une feuille neuve.
 papa|Bravo, Nina.
-papa|C'est du bon travail.
 papa|La peine de Nino reste un peu.
 enfant-f|J'ai dit pardon.
 papa|Oui.
 papa|Et tu as attendu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1788,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La tour grandit tout doucement. Papa reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt; près d'eux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tour grandit tout doucement. Un cube rouge, un cube gris. On reste assis près de Nino ? Oui, papa. La feuille neuve est encore blanche. La peine reste un peu. Je laisse du temps. Oui. C'est bien. Le bocal n'est plus bleu. L'eau est calme. La chaussette grise attend encore. On la remettra plus tard. D'accord, papa.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,7 +1935,6 @@
 enfant-f|D'accord, papa.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1964,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit pardon. J'ai tendu une feuille. Bravo. Tu as fait du bon travail. Le pinceau est sec, maintenant. L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu une feuille. Bravo. Le pinceau est sec, maintenant.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit pardon. J'ai tendu une feuille. Bravo. Le pinceau est sec, maintenant.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,12 +2102,9 @@
           <t>enfant-f|J'ai dit pardon.
 enfant-f|J'ai tendu une feuille.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le pinceau est sec, maintenant.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pinceau est sec, maintenant.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2131,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, table puis cubes</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rania, Nino, papa</t>
+          <t>Nina, Nino, papa</t>
         </is>
       </c>
     </row>
